--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$2:$X$3</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -21,7 +24,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
+  <si>
+    <t xml:space="preserve">Basic Information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Scoring (per Source)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual CVSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety Assessment</t>
+  </si>
   <si>
     <t xml:space="preserve">Risk ID</t>
   </si>
@@ -41,15 +59,6 @@
     <t xml:space="preserve">Published Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Base Scoring (per Source)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual</t>
-  </si>
-  <si>
     <t xml:space="preserve">CVSS</t>
   </si>
   <si>
@@ -92,6 +101,12 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
+    <t xml:space="preserve">Safety Rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network</t>
   </si>
   <si>
@@ -107,28 +122,64 @@
     <t xml:space="preserve">Residual Risk Scoring Details</t>
   </si>
   <si>
+    <t xml:space="preserve">Safety Heatmap</t>
+  </si>
+  <si>
     <t xml:space="preserve">Column Name</t>
   </si>
   <si>
     <t xml:space="preserve">Acceptable Values</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyber Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min CVSS Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical/Catastrophic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Attack Vector (AV)</t>
   </si>
   <si>
     <t xml:space="preserve">Network (0.85), Adjacent (0.62), Local (0.55), Physical (0.2)</t>
   </si>
   <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncontrolled</t>
+  </si>
+  <si>
     <t xml:space="preserve">Attack Complexity (AC)</t>
   </si>
   <si>
     <t xml:space="preserve">Low (0.77), High (0.44)</t>
   </si>
   <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
     <t xml:space="preserve">Privileges Required (PR)</t>
   </si>
   <si>
     <t xml:space="preserve">None (0.85), Low (0.62), High (0.27)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
   </si>
   <si>
     <t xml:space="preserve">User Interaction (UI)</t>
@@ -159,8 +210,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -207,7 +260,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,19 +276,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE0C2CD"/>
-        <bgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF5CE"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE8F2A1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F2A1"/>
         <bgColor rgb="FFFFF5CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA6A6"/>
+        <bgColor rgb="FFE0C2CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -247,7 +306,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFDBB6"/>
-        <bgColor rgb="FFFFF5CE"/>
+        <bgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -292,7 +351,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -325,6 +384,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -337,8 +404,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -353,20 +420,40 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -378,18 +465,101 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF729FCF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0C2CD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF5CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F2A1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFA6A6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FF006600"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFFFCCCC"/>
+      <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF006600"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -417,7 +587,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFE8F2A1"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFA6A6"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFDBB6"/>
       <rgbColor rgb="FF3366FF"/>
@@ -439,6 +609,10 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,13 +726,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="18.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="37.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="50.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="42.19"/>
@@ -568,39 +742,31 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="13" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="3" width="41.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="18.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="19.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
@@ -611,122 +777,156 @@
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
+      <c r="W1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="X1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G2" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="V2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" s="11" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="10" t="s">
+      <c r="W2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="10" t="s">
+      <c r="X2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="U3" s="8" t="str">
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="10" t="str">
         <f aca="false">"CVSS:3.0/AV:"&amp;_xlfn.SWITCH(M3,"Network","N","Adjacent","A","Local","L","Physical","P")&amp;"/AC:"&amp;LEFT(N3,1)&amp;"/PR:"&amp;LEFT(O3,1)&amp;"/UI:"&amp;_xlfn.SWITCH(P3,"None","N","Required","R")&amp;"/S:"&amp;LEFT(Q3,1)&amp;"/C:"&amp;LEFT(R3,1)&amp;"/I:"&amp;LEFT(S3,1)&amp;"/A:"&amp;LEFT(T3,1)</f>
         <v>CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:L</v>
       </c>
-      <c r="V3" s="8" t="n">
+      <c r="V3" s="10" t="n">
         <f aca="false">GET_CVSS(M3, N3, O3, P3, Q3, R3, S3, T3)</f>
         <v>7.3</v>
       </c>
+      <c r="W3" s="12"/>
+      <c r="X3" s="13" t="e">
+        <f aca="false">INDEX(Notes!G4:J7,_xlfn.IFS( V3&gt;=Notes!F4, 1, V3&gt;=Notes!F5, 2, A2&gt;=Notes!F6, 3, A2&lt;"$Notes.F6",4 ),MATCH(W3,Notes!G3:J3,0))</f>
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+  <autoFilter ref="A2:X3"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="M1:V1"/>
+    <mergeCell ref="W1:X1"/>
   </mergeCells>
-  <dataValidations count="6">
+  <conditionalFormatting sqref="X3">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>"Controlled"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X3">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>"Uncontrolled"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M3" type="list">
       <formula1>"Network,Adjacent,Local,Physical"</formula1>
       <formula2>0</formula2>
@@ -751,6 +951,10 @@
       <formula1>"Unchanged,Changed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="W3" type="list">
+      <formula1>Notes!$G$3:$J$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -759,6 +963,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -767,139 +972,241 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="12" width="49.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="49.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="9.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="3" width="13.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="14"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="F7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>39</v>
+      <c r="A8" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>55</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>41</v>
+      <c r="A9" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>57</v>
       </c>
       <c r="D9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>41</v>
+      <c r="A10" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>57</v>
       </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>41</v>
+      <c r="A11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>57</v>
       </c>
       <c r="D11" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:J2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -122,7 +122,7 @@
     <t xml:space="preserve">Residual Risk Scoring Details</t>
   </si>
   <si>
-    <t xml:space="preserve">Safety Heatmap</t>
+    <t xml:space="preserve">Cyber to Safety Heat-Map</t>
   </si>
   <si>
     <t xml:space="preserve">Column Name</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">Negligible</t>
   </si>
   <si>
-    <t xml:space="preserve">Minor</t>
+    <t xml:space="preserve">Minor / Marginal</t>
   </si>
   <si>
     <t xml:space="preserve">Serious</t>
   </si>
   <si>
-    <t xml:space="preserve">Critical/Catastrophic</t>
+    <t xml:space="preserve">Critical / Catastrophic</t>
   </si>
   <si>
     <t xml:space="preserve">Attack Vector (AV)</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">Critical</t>
   </si>
   <si>
+    <t xml:space="preserve">Uncontrolled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Complexity (AC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low (0.77), High (0.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
     <t xml:space="preserve">Controlled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncontrolled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Complexity (AC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low (0.77), High (0.44)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
   </si>
   <si>
     <t xml:space="preserve">Privileges Required (PR)</t>
@@ -260,42 +260,12 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF729FCF"/>
-        <bgColor rgb="FF969696"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0C2CD"/>
-        <bgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF5CE"/>
-        <bgColor rgb="FFE8F2A1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F2A1"/>
-        <bgColor rgb="FFFFF5CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFA6A6"/>
-        <bgColor rgb="FFE0C2CD"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -305,8 +275,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDEDCE6"/>
+        <bgColor rgb="FFFFD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5CE"/>
+        <bgColor rgb="FFF6F9D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9D4"/>
+        <bgColor rgb="FFFFF5CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7D7"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFDBB6"/>
-        <bgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -351,7 +345,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -420,40 +414,36 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -469,7 +459,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF729FCF"/>
+          <fgColor rgb="FFB4C7DC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -484,7 +474,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE0C2CD"/>
+          <fgColor rgb="FFDEDCE6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -508,7 +498,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE8F2A1"/>
+          <fgColor rgb="FFF6F9D4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -516,7 +506,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFA6A6"/>
+          <fgColor rgb="FFFFD7D7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -551,7 +541,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFCCCC"/>
+      <rgbColor rgb="FFFFF5CE"/>
       <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -566,14 +556,14 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF729FCF"/>
+      <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF5CE"/>
+      <rgbColor rgb="FFF6F9D4"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFE0C2CD"/>
+      <rgbColor rgb="FFDEDCE6"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -585,9 +575,9 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFE8F2A1"/>
+      <rgbColor rgb="FFFFD7D7"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFFA6A6"/>
+      <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFDBB6"/>
       <rgbColor rgb="FF3366FF"/>
@@ -1052,17 +1042,17 @@
       <c r="F4" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>45</v>
+      <c r="H4" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1070,29 +1060,29 @@
         <v>18</v>
       </c>
       <c r="B5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>47</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="J5" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1112,17 +1102,17 @@
       <c r="F6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1142,16 +1132,16 @@
       <c r="F7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="25" t="s">
+      <c r="G7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="13" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1208,6 +1198,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
+  <conditionalFormatting sqref="G4:J7">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>"Controlled"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:J7">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>"Uncontrolled"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -1042,16 +1042,16 @@
       <c r="F4" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1072,16 +1072,16 @@
       <c r="F5" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1102,16 +1102,16 @@
       <c r="F6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1132,16 +1132,16 @@
       <c r="F7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1202,8 +1202,6 @@
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"Controlled"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:J7">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Uncontrolled"</formula>
     </cfRule>
